--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\Unity_2DMainProject\2D_MainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
   <si>
     <t>Item_Equip_Hat_1</t>
   </si>
@@ -198,6 +198,54 @@
   </si>
   <si>
     <t>Icon/Icon_Item_Box_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Key_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Letter_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>오래된 편지</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>낡은 열쇠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고대 동전</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고대 문명의 흔적이 새겨진 동전</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>어딘가의 문을 열 수 있을 것 같다..</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐라고 적혀있다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_AncientCoin_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_AncientCoin_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Key_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Letter_1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1040,14 +1088,30 @@
       <c r="M9" s="18"/>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="A10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="4">
+        <v>200</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>50</v>
+      </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -1055,14 +1119,30 @@
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="A11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="4">
+        <v>3</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -1070,14 +1150,30 @@
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="A12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="4">
+        <v>5</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>52</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -19,23 +19,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
-  <si>
-    <t>Item_Equip_Hat_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Corn</t>
-  </si>
-  <si>
-    <t>상자다. 딱히 의미가 있진 않다.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>옥수수다</t>
-  </si>
-  <si>
     <t>(name)</t>
   </si>
   <si>
@@ -51,154 +39,34 @@
     <t>Legend</t>
   </si>
   <si>
-    <t>의문의 모자</t>
-  </si>
-  <si>
     <t>Normal</t>
   </si>
   <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>지역에 나타나는 금화</t>
-  </si>
-  <si>
     <t>ItemType</t>
   </si>
   <si>
     <t>SellingPrice</t>
   </si>
   <si>
-    <t>Item_DummyBox_1</t>
-  </si>
-  <si>
     <t>MaxStackCount</t>
   </si>
   <si>
-    <t>착용하면 공격력이 강해진다.</t>
-  </si>
-  <si>
     <t>캐릭터 전체 컨셉이나 스토리</t>
   </si>
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
   <si>
-    <t>Item_Gold_1</t>
-  </si>
-  <si>
-    <t>Item_Corn_1</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
     <t>IconPath</t>
   </si>
   <si>
-    <t>상자</t>
-  </si>
-  <si>
-    <t>옥수수</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>화폐</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Gold_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Equip_Hat_1</t>
-  </si>
-  <si>
-    <t>감자</t>
-  </si>
-  <si>
-    <t>Item_Potato_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Carrot_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>당근</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Icon/Icon_Item_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Carrot</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Icon/Icon_Item_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Potato</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_1</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>감자다. 딱히 의미가 있진 않다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>당근이다. 딱히 의미가 있진 않다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Box_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Item_Key_1</t>
@@ -331,19 +199,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="0"/>
         <bgColor rgb="FFD86DCD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="0"/>
         <bgColor rgb="FF4D93D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,7 +245,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -387,9 +255,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -843,89 +708,89 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="12.75">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>24</v>
+      <c r="F3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="4">
+        <v>200</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="4">
-        <v>20</v>
-      </c>
-      <c r="G4" s="4">
-        <v>100</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>40</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -934,29 +799,29 @@
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>13</v>
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5" s="4">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="G5" s="4">
-        <v>1000</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>30</v>
+        <v>1</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -966,152 +831,89 @@
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F6" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="4">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>31</v>
+      <c r="H6" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="4">
-        <v>100</v>
-      </c>
-      <c r="G7" s="4">
-        <v>20</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>1</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" s="20" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="18">
-        <v>20</v>
-      </c>
-      <c r="G8" s="18">
-        <v>100</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
-    </row>
-    <row r="9" spans="1:13" s="20" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A9" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="18">
-        <v>5</v>
-      </c>
-      <c r="G9" s="18">
-        <v>500</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
+    <row r="8" spans="1:13" s="19" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+    </row>
+    <row r="9" spans="1:13" s="19" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="4">
-        <v>200</v>
-      </c>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>50</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="14"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -1119,30 +921,14 @@
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="4">
-        <v>3</v>
-      </c>
-      <c r="G11" s="4">
-        <v>1</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>51</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="14"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -1150,30 +936,14 @@
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="4">
-        <v>5</v>
-      </c>
-      <c r="G12" s="4">
-        <v>1</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>52</v>
-      </c>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="14"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -1226,104 +996,104 @@
       <c r="M15" s="4"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:3" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -89,31 +89,31 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>어딘가의 문을 열 수 있을 것 같다..</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_AncientCoin_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_AncientCoin_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Key_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Letter_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>고대 문명의 흔적이 새겨진 동전</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>어딘가의 문을 열 수 있을 것 같다..</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>뭐라고 적혀있다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_AncientCoin_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_AncientCoin_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Key_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Letter_1</t>
+    <t>알 수 없는 글씨로 적혀있다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -769,13 +769,13 @@
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>6</v>
@@ -790,7 +790,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -806,7 +806,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>6</v>
@@ -821,7 +821,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -837,7 +837,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>6</v>
@@ -852,7 +852,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>string</t>
   </si>
@@ -114,6 +114,22 @@
   </si>
   <si>
     <t>알 수 없는 글씨로 적혀있다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Churu_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>츄르</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고양이가 좋아하는 츄르다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Churu_1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -861,14 +877,30 @@
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>31</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t>string</t>
   </si>
@@ -130,6 +130,38 @@
   </si>
   <si>
     <t>Icon/Icon_Item_Churu_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Cat_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>흰고양이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>잃어버린 고양이 첫째</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Cat_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>노랭고양이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Cat_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>잃어버린 고양이 둘째</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Cat_2</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -261,7 +293,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -292,7 +324,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -907,30 +938,62 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" s="19" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
+    <row r="8" spans="1:13" s="18" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="17">
+        <v>1</v>
+      </c>
+      <c r="G8" s="17">
+        <v>1</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
     </row>
-    <row r="9" spans="1:13" s="19" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
+    <row r="9" spans="1:13" s="18" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A9" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="17">
+        <v>1</v>
+      </c>
+      <c r="G9" s="17">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>39</v>
+      </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
